--- a/Bharat/New-Siddharth/siddharth BS.xlsx
+++ b/Bharat/New-Siddharth/siddharth BS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\Bharat\New-Siddharth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F512682F-9E5D-4461-99CB-AF26AF736743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB881747-524C-40C4-955A-AF499119F239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="I&amp;E" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="137">
   <si>
     <t>NEW SIDDHARTH CO-OPERATIVE HOUSING SOCIETY LTD.</t>
   </si>
@@ -460,7 +458,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -676,6 +674,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1388,7 +1398,7 @@
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1936,6 +1946,42 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1951,17 +1997,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1995,9 +2041,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="26" fillId="0" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2053,39 +2096,11 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2410,37 +2425,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="219" t="s">
+      <c r="A1" s="231" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="220"/>
-      <c r="C1" s="220"/>
-      <c r="D1" s="220"/>
-      <c r="E1" s="220"/>
-      <c r="F1" s="220"/>
-      <c r="G1" s="221"/>
+      <c r="B1" s="232"/>
+      <c r="C1" s="232"/>
+      <c r="D1" s="232"/>
+      <c r="E1" s="232"/>
+      <c r="F1" s="232"/>
+      <c r="G1" s="233"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="222" t="s">
+      <c r="A2" s="234" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="222"/>
-      <c r="C2" s="222"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
-      <c r="G2" s="222"/>
+      <c r="B2" s="234"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="234"/>
     </row>
     <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="222" t="s">
+      <c r="A3" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="222"/>
-      <c r="C3" s="222"/>
-      <c r="D3" s="222"/>
-      <c r="E3" s="222"/>
-      <c r="F3" s="222"/>
-      <c r="G3" s="222"/>
+      <c r="B3" s="234"/>
+      <c r="C3" s="234"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
+      <c r="G3" s="234"/>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2783,17 +2798,17 @@
       <c r="G25" s="33"/>
     </row>
     <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="223" t="s">
+      <c r="A26" s="235" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="270"/>
+      <c r="B26" s="236"/>
       <c r="C26" s="30"/>
       <c r="D26" s="30"/>
-      <c r="E26" s="224" t="s">
+      <c r="E26" s="237" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="224"/>
-      <c r="G26" s="225"/>
+      <c r="F26" s="237"/>
+      <c r="G26" s="238"/>
     </row>
     <row r="27" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
@@ -2836,11 +2851,11 @@
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
       <c r="D31" s="34"/>
-      <c r="E31" s="226" t="s">
+      <c r="E31" s="229" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="226"/>
-      <c r="G31" s="227"/>
+      <c r="F31" s="229"/>
+      <c r="G31" s="230"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="37"/>
@@ -2891,52 +2906,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="228" t="s">
+      <c r="A1" s="240" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="229"/>
-      <c r="C1" s="229"/>
-      <c r="D1" s="229"/>
-      <c r="E1" s="229"/>
-      <c r="F1" s="229"/>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="230"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="242"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="231" t="s">
+      <c r="A2" s="243" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="232"/>
-      <c r="C2" s="232"/>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="232"/>
-      <c r="H2" s="232"/>
-      <c r="I2" s="233"/>
+      <c r="B2" s="244"/>
+      <c r="C2" s="244"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="244"/>
+      <c r="I2" s="245"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="234" t="s">
+      <c r="A3" s="246" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="235"/>
-      <c r="C3" s="235"/>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="235"/>
-      <c r="H3" s="235"/>
-      <c r="I3" s="236"/>
+      <c r="B3" s="247"/>
+      <c r="C3" s="247"/>
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="247"/>
+      <c r="I3" s="248"/>
     </row>
     <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="249" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="249"/>
       <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
@@ -3588,10 +3603,10 @@
         <f>SUM(A10:A39)</f>
         <v>5310699.3900000006</v>
       </c>
-      <c r="B40" s="222" t="s">
+      <c r="B40" s="234" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="238"/>
+      <c r="C40" s="250"/>
       <c r="D40" s="113">
         <f>SUM(D9:D39)</f>
         <v>5312625.3900000006</v>
@@ -3735,7 +3750,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Y97"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Y93"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="138" customWidth="1"/>
@@ -3756,17 +3774,20 @@
     <col min="16" max="16" width="10.5546875" style="138" customWidth="1"/>
     <col min="17" max="17" width="9.44140625" style="138" customWidth="1"/>
     <col min="18" max="19" width="10" style="138" customWidth="1"/>
-    <col min="20" max="21" width="23.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="13.5546875" style="138" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.88671875" style="138" customWidth="1"/>
     <col min="22" max="22" width="15.88671875" style="138" hidden="1" customWidth="1"/>
     <col min="23" max="25" width="10.6640625" style="138" hidden="1" customWidth="1"/>
     <col min="26" max="16384" width="14.44140625" style="138"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="137"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
+    <row r="1" spans="1:24" s="272" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="271" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="273"/>
+      <c r="W1" s="273"/>
+      <c r="X1" s="273"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="137" t="s">
@@ -3807,55 +3828,55 @@
       <c r="X3" s="139"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="250" t="s">
+      <c r="A4" s="261" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="250" t="s">
+      <c r="B4" s="261" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="262" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="252" t="s">
+      <c r="D4" s="263" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="245" t="s">
+      <c r="E4" s="256" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="246"/>
-      <c r="G4" s="247"/>
+      <c r="F4" s="257"/>
+      <c r="G4" s="258"/>
       <c r="H4" s="144" t="s">
         <v>90</v>
       </c>
       <c r="I4" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="241" t="s">
+      <c r="J4" s="252" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="241" t="s">
+      <c r="K4" s="252" t="s">
         <v>93</v>
       </c>
-      <c r="L4" s="243" t="s">
+      <c r="L4" s="254" t="s">
         <v>94</v>
       </c>
-      <c r="M4" s="245" t="s">
+      <c r="M4" s="256" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="246"/>
-      <c r="O4" s="247"/>
-      <c r="P4" s="245" t="s">
+      <c r="N4" s="257"/>
+      <c r="O4" s="258"/>
+      <c r="P4" s="256" t="s">
         <v>96</v>
       </c>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="247"/>
-      <c r="S4" s="248" t="s">
+      <c r="Q4" s="257"/>
+      <c r="R4" s="258"/>
+      <c r="S4" s="259" t="s">
         <v>97</v>
       </c>
-      <c r="T4" s="241" t="s">
+      <c r="T4" s="252" t="s">
         <v>98</v>
       </c>
-      <c r="U4" s="240" t="s">
+      <c r="U4" s="251" t="s">
         <v>99</v>
       </c>
       <c r="V4" s="139"/>
@@ -3863,10 +3884,10 @@
       <c r="X4" s="139"/>
     </row>
     <row r="5" spans="1:24" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="242"/>
-      <c r="B5" s="242"/>
-      <c r="C5" s="242"/>
-      <c r="D5" s="253"/>
+      <c r="A5" s="253"/>
+      <c r="B5" s="253"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="264"/>
       <c r="E5" s="148" t="s">
         <v>100</v>
       </c>
@@ -3882,9 +3903,9 @@
       <c r="I5" s="145" t="s">
         <v>104</v>
       </c>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="244"/>
+      <c r="J5" s="253"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="255"/>
       <c r="M5" s="150" t="s">
         <v>100</v>
       </c>
@@ -3903,9 +3924,9 @@
       <c r="R5" s="150" t="s">
         <v>102</v>
       </c>
-      <c r="S5" s="249"/>
-      <c r="T5" s="242"/>
-      <c r="U5" s="240"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="251"/>
       <c r="V5" s="152" t="s">
         <v>107</v>
       </c>
@@ -3914,7 +3935,7 @@
       </c>
       <c r="X5" s="139"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="153"/>
       <c r="B6" s="143"/>
       <c r="C6" s="146"/>
@@ -3940,9 +3961,9 @@
       <c r="W6" s="139"/>
       <c r="X6" s="139"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="159">
-        <f t="shared" ref="A7:A12" si="0">ROW()-5</f>
+        <f t="shared" ref="A7:A11" si="0">ROW()-5</f>
         <v>2</v>
       </c>
       <c r="B7" s="160" t="s">
@@ -3961,7 +3982,7 @@
         <v>21439</v>
       </c>
       <c r="G7" s="178">
-        <f t="shared" ref="G7:G15" si="1">E7+F7</f>
+        <f t="shared" ref="G7:G11" si="1">E7+F7</f>
         <v>1622168</v>
       </c>
       <c r="H7" s="165"/>
@@ -3981,7 +4002,7 @@
       <c r="M7" s="167"/>
       <c r="N7" s="167"/>
       <c r="O7" s="180">
-        <f t="shared" ref="O7:O12" si="2">SUM(M7:N7)</f>
+        <f t="shared" ref="O7:O11" si="2">SUM(M7:N7)</f>
         <v>0</v>
       </c>
       <c r="P7" s="180">
@@ -3993,7 +4014,7 @@
         <v>125147</v>
       </c>
       <c r="R7" s="180">
-        <f t="shared" ref="R7:R15" si="3">Q7+P7</f>
+        <f t="shared" ref="R7:R11" si="3">Q7+P7</f>
         <v>1725876</v>
       </c>
       <c r="S7" s="180" t="s">
@@ -4007,12 +4028,12 @@
         <v>472096</v>
       </c>
       <c r="W7" s="168">
-        <f t="shared" ref="W7:W15" si="4">R7-V7</f>
+        <f t="shared" ref="W7:W11" si="4">R7-V7</f>
         <v>1253780</v>
       </c>
       <c r="X7" s="139"/>
     </row>
-    <row r="8" spans="1:24" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="159">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -4058,13 +4079,10 @@
         <f t="shared" ref="P8:P9" si="6">E8+H8-M8+K8</f>
         <v>500000</v>
       </c>
-      <c r="Q8" s="180">
-        <f t="shared" ref="Q8:Q9" si="7">I8-J8+F8</f>
-        <v>21102</v>
-      </c>
+      <c r="Q8" s="180"/>
       <c r="R8" s="180">
         <f t="shared" si="3"/>
-        <v>521102</v>
+        <v>500000</v>
       </c>
       <c r="S8" s="180" t="s">
         <v>113</v>
@@ -4078,11 +4096,11 @@
       </c>
       <c r="W8" s="168">
         <f t="shared" si="4"/>
-        <v>49006</v>
+        <v>27904</v>
       </c>
       <c r="X8" s="139"/>
     </row>
-    <row r="9" spans="1:24" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="159">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -4128,13 +4146,10 @@
         <f t="shared" si="6"/>
         <v>500000</v>
       </c>
-      <c r="Q9" s="180">
-        <f t="shared" si="7"/>
-        <v>21102</v>
-      </c>
+      <c r="Q9" s="180"/>
       <c r="R9" s="180">
         <f t="shared" si="3"/>
-        <v>521102</v>
+        <v>500000</v>
       </c>
       <c r="S9" s="180" t="s">
         <v>113</v>
@@ -4148,11 +4163,11 @@
       </c>
       <c r="W9" s="168">
         <f t="shared" si="4"/>
-        <v>49006</v>
+        <v>27904</v>
       </c>
       <c r="X9" s="139"/>
     </row>
-    <row r="10" spans="1:24" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="159">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -4217,7 +4232,7 @@
       </c>
       <c r="X10" s="139"/>
     </row>
-    <row r="11" spans="1:24" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="159">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -4252,7 +4267,7 @@
       </c>
       <c r="M11" s="167"/>
       <c r="N11" s="167">
-        <f t="shared" ref="N11" si="8">I11-J11</f>
+        <f t="shared" ref="N11" si="7">I11-J11</f>
         <v>4220</v>
       </c>
       <c r="O11" s="180">
@@ -4260,16 +4275,13 @@
         <v>4220</v>
       </c>
       <c r="P11" s="180">
-        <f t="shared" ref="P11:P15" si="9">E11+H11-M11+K11</f>
+        <f t="shared" ref="P11" si="8">E11+H11-M11+K11</f>
         <v>100000</v>
       </c>
-      <c r="Q11" s="180">
-        <f t="shared" ref="Q11:Q12" si="10">I11-J11+F11</f>
-        <v>4220</v>
-      </c>
+      <c r="Q11" s="180"/>
       <c r="R11" s="180">
         <f t="shared" si="3"/>
-        <v>104220</v>
+        <v>100000</v>
       </c>
       <c r="S11" s="180" t="s">
         <v>113</v>
@@ -4283,321 +4295,224 @@
       </c>
       <c r="W11" s="168">
         <f t="shared" si="4"/>
-        <v>-367876</v>
+        <v>-372096</v>
       </c>
       <c r="X11" s="139"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="159">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B12" s="160"/>
-      <c r="C12" s="161"/>
-      <c r="D12" s="162"/>
-      <c r="E12" s="163"/>
-      <c r="F12" s="164"/>
-      <c r="G12" s="178">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
-      <c r="J12" s="166"/>
-      <c r="K12" s="167"/>
-      <c r="L12" s="162"/>
-      <c r="M12" s="167"/>
-      <c r="N12" s="167"/>
-      <c r="O12" s="180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="180">
+    <row r="12" spans="1:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="171"/>
+      <c r="B12" s="172" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="173"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="172">
+        <f t="shared" ref="E12:K12" si="9">SUM(E7:E11)</f>
+        <v>1600729</v>
+      </c>
+      <c r="F12" s="172">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="180">
+        <v>21439</v>
+      </c>
+      <c r="G12" s="179">
+        <f t="shared" si="9"/>
+        <v>1622168</v>
+      </c>
+      <c r="H12" s="172">
+        <f t="shared" si="9"/>
+        <v>1200000</v>
+      </c>
+      <c r="I12" s="172">
+        <f t="shared" si="9"/>
+        <v>152790</v>
+      </c>
+      <c r="J12" s="172">
+        <f t="shared" si="9"/>
+        <v>25351</v>
+      </c>
+      <c r="K12" s="186">
+        <f t="shared" si="9"/>
+        <v>23140</v>
+      </c>
+      <c r="L12" s="172"/>
+      <c r="M12" s="172">
+        <f t="shared" ref="M12:R12" si="10">SUM(M7:M11)</f>
+        <v>100000</v>
+      </c>
+      <c r="N12" s="172">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="180">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="180"/>
-      <c r="T12" s="181"/>
-      <c r="U12" s="182"/>
-      <c r="V12" s="139">
-        <v>472096</v>
-      </c>
-      <c r="W12" s="168">
-        <f t="shared" si="4"/>
-        <v>-472096</v>
-      </c>
+        <v>46871</v>
+      </c>
+      <c r="O12" s="179">
+        <f t="shared" si="10"/>
+        <v>146871</v>
+      </c>
+      <c r="P12" s="179">
+        <f t="shared" si="10"/>
+        <v>2700729</v>
+      </c>
+      <c r="Q12" s="179">
+        <f t="shared" si="10"/>
+        <v>125147</v>
+      </c>
+      <c r="R12" s="179">
+        <f t="shared" si="10"/>
+        <v>2825876</v>
+      </c>
+      <c r="S12" s="179"/>
+      <c r="T12" s="183"/>
+      <c r="U12" s="184"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="168"/>
       <c r="X12" s="139"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="159">
-        <f>ROW()-5</f>
-        <v>8</v>
-      </c>
-      <c r="B13" s="160"/>
-      <c r="C13" s="161"/>
-      <c r="D13" s="162"/>
-      <c r="E13" s="163"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="178">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="165"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="167"/>
-      <c r="L13" s="162"/>
-      <c r="M13" s="167"/>
-      <c r="N13" s="167"/>
-      <c r="O13" s="180">
-        <f>SUM(M13:N13)</f>
-        <v>0</v>
-      </c>
-      <c r="P13" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="180">
-        <f>I13-J13+F13</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="180">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="180"/>
-      <c r="T13" s="181"/>
-      <c r="U13" s="182"/>
-      <c r="V13" s="139">
-        <v>472096</v>
-      </c>
-      <c r="W13" s="168">
-        <f t="shared" si="4"/>
-        <v>-472096</v>
-      </c>
+    <row r="13" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="174"/>
+      <c r="B13" s="174"/>
+      <c r="C13" s="175"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="174"/>
+      <c r="G13" s="174"/>
+      <c r="H13" s="174"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="174"/>
+      <c r="K13" s="174"/>
+      <c r="L13" s="174"/>
+      <c r="M13" s="174"/>
+      <c r="N13" s="174"/>
+      <c r="O13" s="185"/>
+      <c r="P13" s="185"/>
+      <c r="Q13" s="185"/>
+      <c r="R13" s="185"/>
+      <c r="S13" s="185"/>
+      <c r="T13" s="185"/>
+      <c r="U13" s="185"/>
+      <c r="V13" s="139"/>
+      <c r="W13" s="139"/>
       <c r="X13" s="139"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="159">
-        <f>ROW()-5</f>
-        <v>9</v>
-      </c>
-      <c r="B14" s="160"/>
-      <c r="C14" s="161"/>
-      <c r="D14" s="162"/>
-      <c r="E14" s="163"/>
-      <c r="F14" s="164"/>
-      <c r="G14" s="178">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="170"/>
-      <c r="I14" s="166"/>
-      <c r="J14" s="166"/>
-      <c r="K14" s="167"/>
-      <c r="L14" s="162"/>
-      <c r="M14" s="167"/>
-      <c r="N14" s="167"/>
-      <c r="O14" s="180">
-        <f>SUM(M14:N14)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="180">
-        <f t="shared" ref="Q14:Q15" si="11">F14+I14-J14-N14</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="180">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="180"/>
-      <c r="T14" s="181"/>
-      <c r="U14" s="182"/>
-      <c r="V14" s="139">
-        <v>472096</v>
-      </c>
-      <c r="W14" s="168">
-        <f t="shared" si="4"/>
-        <v>-472096</v>
-      </c>
+      <c r="A14" s="174"/>
+      <c r="B14" s="174"/>
+      <c r="C14" s="175"/>
+      <c r="D14" s="175"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="174"/>
+      <c r="G14" s="174"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="176"/>
+      <c r="J14" s="174"/>
+      <c r="K14" s="174"/>
+      <c r="L14" s="174"/>
+      <c r="M14" s="174"/>
+      <c r="N14" s="174"/>
+      <c r="O14" s="174"/>
+      <c r="P14" s="174"/>
+      <c r="Q14" s="174"/>
+      <c r="R14" s="174"/>
+      <c r="S14" s="174"/>
+      <c r="T14" s="174"/>
+      <c r="U14" s="174"/>
+      <c r="V14" s="139"/>
+      <c r="W14" s="139"/>
       <c r="X14" s="139"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="159">
-        <f t="shared" ref="A15" si="12">ROW()-5</f>
-        <v>10</v>
-      </c>
-      <c r="B15" s="160"/>
-      <c r="C15" s="161"/>
-      <c r="D15" s="162"/>
-      <c r="E15" s="163"/>
-      <c r="F15" s="164"/>
-      <c r="G15" s="178">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="170"/>
-      <c r="I15" s="166"/>
-      <c r="J15" s="166"/>
-      <c r="K15" s="167"/>
-      <c r="L15" s="162"/>
-      <c r="M15" s="167"/>
-      <c r="N15" s="167"/>
-      <c r="O15" s="180">
-        <f>SUM(M15:N15)</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="180">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="180">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="180"/>
-      <c r="T15" s="181"/>
-      <c r="U15" s="182"/>
-      <c r="V15" s="139">
-        <v>248174</v>
-      </c>
-      <c r="W15" s="168">
-        <f t="shared" si="4"/>
-        <v>-248174</v>
-      </c>
+      <c r="A15" s="139"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="177"/>
+      <c r="D15" s="177"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="168"/>
+      <c r="J15" s="168"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
+      <c r="U15" s="139"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="139"/>
       <c r="X15" s="139"/>
     </row>
-    <row r="16" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="171"/>
-      <c r="B16" s="172" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="173"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="172">
-        <f t="shared" ref="E16:F16" si="13">SUM(E7:E15)</f>
-        <v>1600729</v>
-      </c>
-      <c r="F16" s="172">
-        <f t="shared" si="13"/>
-        <v>21439</v>
-      </c>
-      <c r="G16" s="179">
-        <f>SUM(G7:G15)</f>
-        <v>1622168</v>
-      </c>
-      <c r="H16" s="172">
-        <f t="shared" ref="H16:R16" si="14">SUM(H7:H15)</f>
-        <v>1200000</v>
-      </c>
-      <c r="I16" s="172">
-        <f t="shared" si="14"/>
-        <v>152790</v>
-      </c>
-      <c r="J16" s="172">
-        <f t="shared" si="14"/>
-        <v>25351</v>
-      </c>
-      <c r="K16" s="186">
-        <f t="shared" si="14"/>
-        <v>23140</v>
-      </c>
-      <c r="L16" s="172"/>
-      <c r="M16" s="172">
-        <f t="shared" si="14"/>
-        <v>100000</v>
-      </c>
-      <c r="N16" s="172">
-        <f t="shared" si="14"/>
-        <v>46871</v>
-      </c>
-      <c r="O16" s="179">
-        <f t="shared" si="14"/>
-        <v>146871</v>
-      </c>
-      <c r="P16" s="179">
-        <f t="shared" si="14"/>
-        <v>2700729</v>
-      </c>
-      <c r="Q16" s="179">
-        <f t="shared" si="14"/>
-        <v>171571</v>
-      </c>
-      <c r="R16" s="179">
-        <f t="shared" si="14"/>
-        <v>2872300</v>
-      </c>
-      <c r="S16" s="179"/>
-      <c r="T16" s="183"/>
-      <c r="U16" s="184"/>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A16" s="139"/>
+      <c r="B16" s="139"/>
+      <c r="C16" s="177"/>
+      <c r="D16" s="177"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="168"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="139"/>
+      <c r="M16" s="139"/>
+      <c r="N16" s="139"/>
+      <c r="O16" s="139"/>
+      <c r="P16" s="139"/>
+      <c r="Q16" s="139"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="139"/>
+      <c r="T16" s="139"/>
+      <c r="U16" s="139"/>
       <c r="V16" s="139"/>
-      <c r="W16" s="168"/>
+      <c r="W16" s="139"/>
       <c r="X16" s="139"/>
     </row>
-    <row r="17" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="174"/>
-      <c r="B17" s="174"/>
-      <c r="C17" s="175"/>
-      <c r="D17" s="175"/>
-      <c r="E17" s="176"/>
-      <c r="F17" s="174"/>
-      <c r="G17" s="174"/>
-      <c r="H17" s="174"/>
-      <c r="I17" s="176"/>
-      <c r="J17" s="174"/>
-      <c r="K17" s="174"/>
-      <c r="L17" s="174"/>
-      <c r="M17" s="174"/>
-      <c r="N17" s="174"/>
-      <c r="O17" s="185"/>
-      <c r="P17" s="185"/>
-      <c r="Q17" s="185"/>
-      <c r="R17" s="185"/>
-      <c r="S17" s="185"/>
-      <c r="T17" s="185"/>
-      <c r="U17" s="185"/>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A17" s="139"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="139"/>
+      <c r="I17" s="168"/>
+      <c r="J17" s="168"/>
+      <c r="K17" s="139"/>
+      <c r="L17" s="139"/>
+      <c r="M17" s="139"/>
+      <c r="N17" s="139"/>
+      <c r="O17" s="139"/>
+      <c r="P17" s="139"/>
+      <c r="Q17" s="168"/>
+      <c r="R17" s="139"/>
+      <c r="S17" s="139"/>
+      <c r="T17" s="139"/>
+      <c r="U17" s="139"/>
       <c r="V17" s="139"/>
       <c r="W17" s="139"/>
       <c r="X17" s="139"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A18" s="174"/>
-      <c r="B18" s="174"/>
-      <c r="C18" s="175"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="176"/>
-      <c r="F18" s="174"/>
-      <c r="G18" s="174"/>
-      <c r="H18" s="174"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="174"/>
-      <c r="K18" s="174"/>
-      <c r="L18" s="174"/>
-      <c r="M18" s="174"/>
-      <c r="N18" s="174"/>
-      <c r="O18" s="174"/>
-      <c r="P18" s="174"/>
-      <c r="Q18" s="174"/>
-      <c r="R18" s="174"/>
-      <c r="S18" s="174"/>
-      <c r="T18" s="174"/>
-      <c r="U18" s="174"/>
+      <c r="A18" s="139"/>
+      <c r="B18" s="139"/>
+      <c r="C18" s="177"/>
+      <c r="D18" s="177"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
+      <c r="S18" s="139"/>
+      <c r="T18" s="139"/>
+      <c r="U18" s="139"/>
       <c r="V18" s="139"/>
       <c r="W18" s="139"/>
       <c r="X18" s="139"/>
@@ -4611,8 +4526,8 @@
       <c r="F19" s="139"/>
       <c r="G19" s="139"/>
       <c r="H19" s="139"/>
-      <c r="I19" s="168"/>
-      <c r="J19" s="168"/>
+      <c r="I19" s="139"/>
+      <c r="J19" s="139"/>
       <c r="K19" s="139"/>
       <c r="L19" s="139"/>
       <c r="M19" s="139"/>
@@ -4656,17 +4571,22 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="139"/>
+      <c r="B21" s="139"/>
+      <c r="C21" s="177"/>
+      <c r="D21" s="177"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
       <c r="G21" s="139"/>
       <c r="H21" s="139"/>
       <c r="I21" s="168"/>
-      <c r="J21" s="168"/>
+      <c r="J21" s="139"/>
       <c r="K21" s="139"/>
       <c r="L21" s="139"/>
       <c r="M21" s="139"/>
       <c r="N21" s="139"/>
       <c r="O21" s="139"/>
       <c r="P21" s="139"/>
-      <c r="Q21" s="168"/>
+      <c r="Q21" s="139"/>
       <c r="R21" s="139"/>
       <c r="S21" s="139"/>
       <c r="T21" s="139"/>
@@ -4710,7 +4630,7 @@
       <c r="F23" s="139"/>
       <c r="G23" s="139"/>
       <c r="H23" s="139"/>
-      <c r="I23" s="139"/>
+      <c r="I23" s="168"/>
       <c r="J23" s="139"/>
       <c r="K23" s="139"/>
       <c r="L23" s="139"/>
@@ -4762,7 +4682,7 @@
       <c r="F25" s="139"/>
       <c r="G25" s="139"/>
       <c r="H25" s="139"/>
-      <c r="I25" s="168"/>
+      <c r="I25" s="139"/>
       <c r="J25" s="139"/>
       <c r="K25" s="139"/>
       <c r="L25" s="139"/>
@@ -4814,7 +4734,7 @@
       <c r="F27" s="139"/>
       <c r="G27" s="139"/>
       <c r="H27" s="139"/>
-      <c r="I27" s="168"/>
+      <c r="I27" s="139"/>
       <c r="J27" s="139"/>
       <c r="K27" s="139"/>
       <c r="L27" s="139"/>
@@ -4840,7 +4760,7 @@
       <c r="F28" s="139"/>
       <c r="G28" s="139"/>
       <c r="H28" s="139"/>
-      <c r="I28" s="168"/>
+      <c r="I28" s="139"/>
       <c r="J28" s="139"/>
       <c r="K28" s="139"/>
       <c r="L28" s="139"/>
@@ -6547,110 +6467,6 @@
       <c r="W93" s="139"/>
       <c r="X93" s="139"/>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A94" s="139"/>
-      <c r="B94" s="139"/>
-      <c r="C94" s="177"/>
-      <c r="D94" s="177"/>
-      <c r="E94" s="139"/>
-      <c r="F94" s="139"/>
-      <c r="G94" s="139"/>
-      <c r="H94" s="139"/>
-      <c r="I94" s="139"/>
-      <c r="J94" s="139"/>
-      <c r="K94" s="139"/>
-      <c r="L94" s="139"/>
-      <c r="M94" s="139"/>
-      <c r="N94" s="139"/>
-      <c r="O94" s="139"/>
-      <c r="P94" s="139"/>
-      <c r="Q94" s="139"/>
-      <c r="R94" s="139"/>
-      <c r="S94" s="139"/>
-      <c r="T94" s="139"/>
-      <c r="U94" s="139"/>
-      <c r="V94" s="139"/>
-      <c r="W94" s="139"/>
-      <c r="X94" s="139"/>
-    </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A95" s="139"/>
-      <c r="B95" s="139"/>
-      <c r="C95" s="177"/>
-      <c r="D95" s="177"/>
-      <c r="E95" s="139"/>
-      <c r="F95" s="139"/>
-      <c r="G95" s="139"/>
-      <c r="H95" s="139"/>
-      <c r="I95" s="139"/>
-      <c r="J95" s="139"/>
-      <c r="K95" s="139"/>
-      <c r="L95" s="139"/>
-      <c r="M95" s="139"/>
-      <c r="N95" s="139"/>
-      <c r="O95" s="139"/>
-      <c r="P95" s="139"/>
-      <c r="Q95" s="139"/>
-      <c r="R95" s="139"/>
-      <c r="S95" s="139"/>
-      <c r="T95" s="139"/>
-      <c r="U95" s="139"/>
-      <c r="V95" s="139"/>
-      <c r="W95" s="139"/>
-      <c r="X95" s="139"/>
-    </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A96" s="139"/>
-      <c r="B96" s="139"/>
-      <c r="C96" s="177"/>
-      <c r="D96" s="177"/>
-      <c r="E96" s="139"/>
-      <c r="F96" s="139"/>
-      <c r="G96" s="139"/>
-      <c r="H96" s="139"/>
-      <c r="I96" s="139"/>
-      <c r="J96" s="139"/>
-      <c r="K96" s="139"/>
-      <c r="L96" s="139"/>
-      <c r="M96" s="139"/>
-      <c r="N96" s="139"/>
-      <c r="O96" s="139"/>
-      <c r="P96" s="139"/>
-      <c r="Q96" s="139"/>
-      <c r="R96" s="139"/>
-      <c r="S96" s="139"/>
-      <c r="T96" s="139"/>
-      <c r="U96" s="139"/>
-      <c r="V96" s="139"/>
-      <c r="W96" s="139"/>
-      <c r="X96" s="139"/>
-    </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A97" s="139"/>
-      <c r="B97" s="139"/>
-      <c r="C97" s="177"/>
-      <c r="D97" s="177"/>
-      <c r="E97" s="139"/>
-      <c r="F97" s="139"/>
-      <c r="G97" s="139"/>
-      <c r="H97" s="139"/>
-      <c r="I97" s="139"/>
-      <c r="J97" s="139"/>
-      <c r="K97" s="139"/>
-      <c r="L97" s="139"/>
-      <c r="M97" s="139"/>
-      <c r="N97" s="139"/>
-      <c r="O97" s="139"/>
-      <c r="P97" s="139"/>
-      <c r="Q97" s="139"/>
-      <c r="R97" s="139"/>
-      <c r="S97" s="139"/>
-      <c r="T97" s="139"/>
-      <c r="U97" s="139"/>
-      <c r="V97" s="139"/>
-      <c r="W97" s="139"/>
-      <c r="X97" s="139"/>
-    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="J4:J5"/>
@@ -6667,7 +6483,9 @@
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="T4:T5"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6686,26 +6504,26 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:8" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="B2" s="254" t="s">
+      <c r="B2" s="265" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="255"/>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256"/>
+      <c r="C2" s="266"/>
+      <c r="D2" s="266"/>
+      <c r="E2" s="266"/>
+      <c r="F2" s="266"/>
+      <c r="G2" s="266"/>
+      <c r="H2" s="267"/>
     </row>
     <row r="3" spans="2:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="B3" s="257" t="s">
+      <c r="B3" s="268" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="258"/>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259"/>
+      <c r="C3" s="269"/>
+      <c r="D3" s="269"/>
+      <c r="E3" s="269"/>
+      <c r="F3" s="269"/>
+      <c r="G3" s="269"/>
+      <c r="H3" s="270"/>
     </row>
     <row r="4" spans="2:8" ht="52.8" x14ac:dyDescent="0.3">
       <c r="B4" s="187" t="s">
@@ -6933,20 +6751,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="224" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="266"/>
-      <c r="C1" s="266"/>
-      <c r="D1" s="266"/>
-      <c r="E1" s="267"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="225"/>
+      <c r="E1" s="226"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="227" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="269"/>
-      <c r="C2" s="269"/>
+      <c r="B2" s="228"/>
+      <c r="C2" s="228"/>
       <c r="D2" s="202" t="s">
         <v>130</v>
       </c>
@@ -6955,10 +6773,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="260" t="s">
+      <c r="A3" s="219" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="261"/>
+      <c r="B3" s="220"/>
       <c r="C3" s="204"/>
       <c r="D3" s="14"/>
       <c r="E3" s="205">
@@ -7010,32 +6828,32 @@
       <c r="E9" s="217"/>
     </row>
     <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="262" t="s">
+      <c r="A10" s="221" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="263"/>
-      <c r="C10" s="263"/>
-      <c r="D10" s="264"/>
+      <c r="B10" s="222"/>
+      <c r="C10" s="222"/>
+      <c r="D10" s="223"/>
       <c r="E10" s="218">
         <f>E3</f>
         <v>128240.79</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="265" t="s">
+      <c r="A12" s="224" t="s">
         <v>136</v>
       </c>
-      <c r="B12" s="266"/>
-      <c r="C12" s="266"/>
-      <c r="D12" s="266"/>
-      <c r="E12" s="267"/>
+      <c r="B12" s="225"/>
+      <c r="C12" s="225"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="226"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="268" t="s">
+      <c r="A13" s="227" t="s">
         <v>129</v>
       </c>
-      <c r="B13" s="269"/>
-      <c r="C13" s="269"/>
+      <c r="B13" s="228"/>
+      <c r="C13" s="228"/>
       <c r="D13" s="202" t="s">
         <v>130</v>
       </c>
@@ -7044,10 +6862,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="260" t="s">
+      <c r="A14" s="219" t="s">
         <v>132</v>
       </c>
-      <c r="B14" s="261"/>
+      <c r="B14" s="220"/>
       <c r="C14" s="204"/>
       <c r="D14" s="14"/>
       <c r="E14" s="205">
@@ -7099,12 +6917,12 @@
       <c r="E20" s="217"/>
     </row>
     <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="262" t="s">
+      <c r="A21" s="221" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="263"/>
-      <c r="C21" s="263"/>
-      <c r="D21" s="264"/>
+      <c r="B21" s="222"/>
+      <c r="C21" s="222"/>
+      <c r="D21" s="223"/>
       <c r="E21" s="218">
         <f>E14</f>
         <v>62162.1</v>
